--- a/Result/profitability/1201.xlsx
+++ b/Result/profitability/1201.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.15625</v>
       </c>
       <c r="N2" t="n">
-        <v>27.91375</v>
+        <v>27.72375</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.31</v>
       </c>
       <c r="M3" t="n">
-        <v>0.16</v>
+        <v>0.17875</v>
       </c>
       <c r="N3" t="n">
-        <v>28.6325</v>
+        <v>28.55125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.24</v>
       </c>
       <c r="M4" t="n">
-        <v>0.17375</v>
+        <v>0.18125</v>
       </c>
       <c r="N4" t="n">
-        <v>29.1</v>
+        <v>28.83875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1775</v>
+        <v>0.20625</v>
       </c>
       <c r="N5" t="n">
-        <v>29.75</v>
+        <v>29.5625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>0.21375</v>
+        <v>0.22875</v>
       </c>
       <c r="N6" t="n">
-        <v>30.96875</v>
+        <v>30.89</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>0.23375</v>
+        <v>0.2725</v>
       </c>
       <c r="N7" t="n">
-        <v>32.04875</v>
+        <v>31.94125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="N8" t="n">
-        <v>33.205</v>
+        <v>33.01625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.31625</v>
       </c>
       <c r="N10" t="n">
-        <v>34.5525</v>
+        <v>34.55249999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1201</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5445</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4035</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1410</v>
+      </c>
+      <c r="F75" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-85</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.56%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>168</v>
+      </c>
+      <c r="J75" t="n">
+        <v>83</v>
+      </c>
+      <c r="K75" t="n">
+        <v>142</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.16125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.995</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.08000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.510000000000002</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.055089383436702</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.600000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.05474452554744524</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
